--- a/output/2026年4月/党费收缴子表/2026年4月-2026年计算机科学与技术学院研究生第七党支部-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-2026年计算机科学与技术学院研究生第七党支部-党费收缴子表.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>姓 名</t>
+          <t>付周</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -628,11 +628,11 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>付周</t>
+          <t>杨明欣</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
@@ -677,11 +677,11 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>杨明欣</t>
+          <t>李悦</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -726,11 +726,11 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>李悦</t>
+          <t>吴春鹏</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -775,11 +775,11 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吴春鹏</t>
+          <t>张光辉</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -824,11 +824,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>张光辉</t>
+          <t>陈忻雅</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
@@ -873,11 +873,11 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陈忻雅</t>
+          <t>段家琪</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -922,11 +922,11 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>段家琪</t>
+          <t>胡月</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -971,11 +971,11 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>胡月</t>
+          <t>李嵩林</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1020,11 +1020,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>李嵩林</t>
+          <t>刘浩</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
@@ -1069,11 +1069,11 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>刘浩</t>
+          <t>马正堂</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1118,11 +1118,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>马正堂</t>
+          <t>莫龙飞</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
@@ -1167,11 +1167,11 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>莫龙飞</t>
+          <t>孙李旭</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1216,11 +1216,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>孙李旭</t>
+          <t>杨若彤</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
@@ -1265,11 +1265,11 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>杨若彤</t>
+          <t>李昕晖</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -1314,11 +1314,11 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>李昕晖</t>
+          <t>何世玉</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -1363,11 +1363,11 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>何世玉</t>
+          <t>牛森</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -1412,11 +1412,11 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>牛森</t>
+          <t>马超</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
@@ -1461,11 +1461,11 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>马超</t>
+          <t>陈鹏程</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -1510,11 +1510,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>陈鹏程</t>
+          <t>崔璨</t>
         </is>
       </c>
       <c r="C23" s="6" t="n">
@@ -1559,11 +1559,11 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>崔璨</t>
+          <t>闫阳阳</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -1608,11 +1608,11 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>闫阳阳</t>
+          <t>李晓华</t>
         </is>
       </c>
       <c r="C25" s="6" t="n">
@@ -1657,11 +1657,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>李晓华</t>
+          <t>王新程</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -1706,11 +1706,11 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>王新程</t>
+          <t>周旭光</t>
         </is>
       </c>
       <c r="C27" s="6" t="n">
@@ -1755,11 +1755,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>周旭光</t>
+          <t>任梓潼</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -1804,11 +1804,11 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>任梓潼</t>
+          <t>李梦倩</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -1853,11 +1853,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>李梦倩</t>
+          <t>郭展宏</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -1902,11 +1902,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>郭展宏</t>
+          <t>高天宇</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -1951,11 +1951,11 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>高天宇</t>
+          <t>吴铭涛</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -2000,11 +2000,11 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>吴铭涛</t>
+          <t>康生国</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -2049,11 +2049,11 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>康生国</t>
+          <t>王鹏</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -2098,7 +2098,7 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -2196,11 +2196,11 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>王鹏</t>
+          <t>常晨洁</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
@@ -2245,11 +2245,11 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>常晨洁</t>
+          <t>刘沛</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -2294,11 +2294,11 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>刘沛</t>
+          <t>郝琴</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
@@ -2343,11 +2343,11 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>郝琴</t>
+          <t>宋志达</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -2392,11 +2392,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>宋志达</t>
+          <t>何晓宇</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
@@ -2441,11 +2441,11 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>何晓宇</t>
+          <t>杨耀威</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -2490,11 +2490,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>杨耀威</t>
+          <t>何世玉</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -2539,11 +2539,11 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>何世玉</t>
+          <t>陈忻雅</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -2588,11 +2588,11 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>陈忻雅</t>
+          <t>段家琪</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -2637,11 +2637,11 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>段家琪</t>
+          <t>韩雷</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -2686,11 +2686,11 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>韩雷</t>
+          <t>胡月</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
@@ -2735,11 +2735,11 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>胡月</t>
+          <t>李昕晖</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -2784,11 +2784,11 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>李昕晖</t>
+          <t>刘浩</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
@@ -2833,11 +2833,11 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>刘浩</t>
+          <t>莫龙飞</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
@@ -2882,11 +2882,11 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>莫龙飞</t>
+          <t>牛森</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
@@ -2931,11 +2931,11 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>牛森</t>
+          <t>孙华键</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -2980,11 +2980,11 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>孙华键</t>
+          <t>孙李旭</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
@@ -3029,11 +3029,11 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>孙李旭</t>
+          <t>王振华</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -3078,11 +3078,11 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>王振华</t>
+          <t>杨若彤</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
@@ -3127,11 +3127,11 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>杨若彤</t>
+          <t>李嵩林</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -3176,11 +3176,11 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>李嵩林</t>
+          <t>马正堂</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
@@ -3225,11 +3225,11 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>马正堂</t>
+          <t>马超</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
@@ -3274,11 +3274,11 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>马超</t>
+          <t>顾泽源</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
@@ -3323,11 +3323,11 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>顾泽源</t>
+          <t>陈鹏程</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
@@ -3372,11 +3372,11 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>陈鹏程</t>
+          <t>英迪</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
@@ -3421,11 +3421,11 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>英迪</t>
+          <t>崔璨</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
@@ -3470,11 +3470,11 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>崔璨</t>
+          <t>王元旭</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
@@ -3519,11 +3519,11 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>王元旭</t>
+          <t>苏兆兆</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
@@ -3568,11 +3568,11 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>苏兆兆</t>
+          <t>闫阳阳</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
@@ -3617,11 +3617,11 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>闫阳阳</t>
+          <t>李晓华</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
@@ -3666,11 +3666,11 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>李晓华</t>
+          <t>王新程</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
@@ -3715,11 +3715,11 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>王新程</t>
+          <t>周旭光</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
@@ -3764,11 +3764,11 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>周旭光</t>
+          <t>任梓潼</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -3813,11 +3813,11 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>任梓潼</t>
+          <t>李梦倩</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
@@ -3862,11 +3862,11 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>李梦倩</t>
+          <t>郭展宏</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
@@ -3911,11 +3911,11 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>郭展宏</t>
+          <t>高天宇</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -3960,11 +3960,11 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>高天宇</t>
+          <t>吴涛鸣</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
@@ -4009,11 +4009,11 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>吴涛鸣</t>
+          <t>康生国</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
@@ -4058,11 +4058,11 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>康生国</t>
+          <t>王宽</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
@@ -4107,11 +4107,11 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>王宽</t>
+          <t>马赛赛</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -4155,83 +4155,34 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>马赛赛</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
-      <c r="L78" s="8" t="n"/>
-      <c r="M78" s="8" t="n"/>
-      <c r="N78" s="8" t="n"/>
-      <c r="O78" s="3" t="n">
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="8" t="n"/>
+      <c r="O77" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A77:N77"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:N2"/>
-    <mergeCell ref="A78:N78"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
